--- a/data/trans_camb/IP09-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP09-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 42,49</t>
+          <t>-26,54; 40,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,9; 48,58</t>
+          <t>-30,48; 50,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,59; 34,46</t>
+          <t>-30,56; 38,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 38,13</t>
+          <t>-11,0; 42,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 51,21</t>
+          <t>-7,05; 53,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,67; 24,0</t>
+          <t>-33,3; 22,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 33,33</t>
+          <t>-7,76; 33,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 41,19</t>
+          <t>-6,75; 40,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-26,2; 19,46</t>
+          <t>-25,87; 19,74</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-54,81; 456,04</t>
+          <t>-56,64; 429,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-64,47; 463,83</t>
+          <t>-68,28; 470,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,99; 370,09</t>
+          <t>-66,39; 408,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,34; 371,29</t>
+          <t>-36,11; 372,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,96; 435,63</t>
+          <t>-23,24; 596,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-87,0; 150,57</t>
+          <t>-85,83; 146,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 212,1</t>
+          <t>-22,46; 235,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 258,48</t>
+          <t>-20,08; 275,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-68,33; 116,51</t>
+          <t>-69,94; 108,3</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 30,04</t>
+          <t>-15,36; 30,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 37,15</t>
+          <t>-14,01; 34,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 59,98</t>
+          <t>-6,66; 60,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 15,33</t>
+          <t>-26,14; 16,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 30,62</t>
+          <t>-15,59; 30,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 31,59</t>
+          <t>-12,0; 33,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 16,16</t>
+          <t>-13,33; 14,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 25,99</t>
+          <t>-8,19; 24,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 38,09</t>
+          <t>-1,05; 42,15</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,97; 239,67</t>
+          <t>-37,36; 216,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,31; 298,28</t>
+          <t>-35,29; 228,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,0; 571,28</t>
+          <t>-26,79; 501,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-60,85; 69,82</t>
+          <t>-59,54; 76,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,95; 125,43</t>
+          <t>-37,72; 134,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,58; 142,76</t>
+          <t>-28,61; 146,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,78; 70,86</t>
+          <t>-34,92; 63,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,15; 116,86</t>
+          <t>-22,17; 102,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 158,5</t>
+          <t>-8,33; 182,99</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-33,99; 27,76</t>
+          <t>-34,96; 27,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-44,04; 28,41</t>
+          <t>-42,79; 26,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-42,66; 25,94</t>
+          <t>-43,41; 26,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 43,56</t>
+          <t>-0,05; 43,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 59,36</t>
+          <t>2,05; 61,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 38,05</t>
+          <t>-13,45; 37,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 32,72</t>
+          <t>-5,92; 32,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 36,91</t>
+          <t>-7,25; 38,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 26,44</t>
+          <t>-16,47; 24,05</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-58,4; 175,52</t>
+          <t>-55,97; 162,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-75,87; 161,64</t>
+          <t>-73,76; 147,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,73; 149,7</t>
+          <t>-75,21; 162,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 805,76</t>
+          <t>-8,84; 837,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 952,37</t>
+          <t>-17,49; 1226,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,16; 684,45</t>
+          <t>-62,01; 587,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,4; 258,66</t>
+          <t>-17,91; 222,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-25,61; 234,67</t>
+          <t>-24,12; 261,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-42,44; 183,67</t>
+          <t>-46,85; 164,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 30,9</t>
+          <t>-8,06; 31,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,14; 65,9</t>
+          <t>8,2; 67,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 42,49</t>
+          <t>-3,01; 43,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-28,33; 15,98</t>
+          <t>-27,18; 16,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 47,08</t>
+          <t>-9,32; 45,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,09; 12,28</t>
+          <t>-29,13; 12,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 18,84</t>
+          <t>-11,2; 19,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,03; 49,29</t>
+          <t>10,14; 50,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 18,79</t>
+          <t>-10,24; 20,59</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-55,06; 751,01</t>
+          <t>-60,44; 938,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,66; 2072,78</t>
+          <t>25,39; 1769,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,64; 1119,89</t>
+          <t>-48,07; 1141,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-58,93; 69,09</t>
+          <t>-57,39; 75,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,23; 196,15</t>
+          <t>-19,29; 190,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,67; 54,39</t>
+          <t>-64,55; 50,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,36; 122,65</t>
+          <t>-36,19; 139,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>25,83; 299,83</t>
+          <t>31,47; 297,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-40,84; 110,75</t>
+          <t>-34,97; 136,01</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 24,55</t>
+          <t>-0,71; 23,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,15; 30,69</t>
+          <t>3,92; 31,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,44; 33,59</t>
+          <t>1,71; 36,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 15,9</t>
+          <t>-6,24; 15,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,46; 30,91</t>
+          <t>4,58; 30,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 13,15</t>
+          <t>-12,25; 12,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 16,68</t>
+          <t>-1,39; 15,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,24; 28,02</t>
+          <t>6,05; 26,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 18,29</t>
+          <t>-3,49; 17,74</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 162,37</t>
+          <t>-3,05; 147,02</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8,12; 191,37</t>
+          <t>10,14; 185,73</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 199,92</t>
+          <t>2,11; 214,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 67,06</t>
+          <t>-17,27; 68,12</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>6,96; 132,31</t>
+          <t>12,38; 127,46</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-37,31; 55,18</t>
+          <t>-36,24; 52,1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 79,17</t>
+          <t>-4,63; 70,76</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>22,02; 125,12</t>
+          <t>20,67; 120,79</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 83,37</t>
+          <t>-11,99; 76,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP09-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP09-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-26,54; 40,54</t>
+          <t>-24,8; 41,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-30,48; 50,18</t>
+          <t>-28,94; 48,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,56; 38,14</t>
+          <t>-27,44; 36,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 42,15</t>
+          <t>-10,85; 40,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 53,65</t>
+          <t>-7,22; 51,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,3; 22,27</t>
+          <t>-33,27; 21,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 33,8</t>
+          <t>-5,88; 33,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 40,65</t>
+          <t>-6,06; 40,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 19,74</t>
+          <t>-26,25; 18,02</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-56,64; 429,38</t>
+          <t>-55,02; 478,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-68,28; 470,12</t>
+          <t>-66,85; 548,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-66,39; 408,85</t>
+          <t>-60,57; 409,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,11; 372,17</t>
+          <t>-35,08; 390,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,24; 596,84</t>
+          <t>-28,02; 476,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,83; 146,58</t>
+          <t>-85,48; 139,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,46; 235,2</t>
+          <t>-19,4; 229,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,08; 275,38</t>
+          <t>-18,54; 254,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,94; 108,3</t>
+          <t>-70,19; 99,24</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 30,46</t>
+          <t>-16,71; 27,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 34,18</t>
+          <t>-12,42; 34,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 60,97</t>
+          <t>-9,49; 58,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 16,06</t>
+          <t>-24,85; 14,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 30,6</t>
+          <t>-16,19; 30,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 33,42</t>
+          <t>-11,55; 32,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 14,67</t>
+          <t>-13,84; 16,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 24,25</t>
+          <t>-8,5; 26,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 42,15</t>
+          <t>-2,08; 38,67</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,36; 216,54</t>
+          <t>-41,27; 196,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,29; 228,86</t>
+          <t>-32,22; 231,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,79; 501,31</t>
+          <t>-35,58; 599,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-59,54; 76,06</t>
+          <t>-59,51; 66,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,72; 134,03</t>
+          <t>-38,6; 137,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,61; 146,27</t>
+          <t>-30,18; 147,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,92; 63,37</t>
+          <t>-36,44; 72,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 102,74</t>
+          <t>-23,01; 116,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 182,99</t>
+          <t>-8,04; 182,76</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-34,96; 27,41</t>
+          <t>-33,77; 29,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-42,79; 26,4</t>
+          <t>-42,51; 30,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-43,41; 26,69</t>
+          <t>-41,55; 26,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 43,46</t>
+          <t>-0,49; 42,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 61,26</t>
+          <t>-0,15; 59,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 37,67</t>
+          <t>-11,72; 39,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 32,71</t>
+          <t>-4,56; 33,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 38,76</t>
+          <t>-8,88; 35,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 24,05</t>
+          <t>-13,62; 27,55</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-55,97; 162,06</t>
+          <t>-55,38; 183,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-73,76; 147,96</t>
+          <t>-76,75; 167,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-75,21; 162,18</t>
+          <t>-72,0; 168,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 837,96</t>
+          <t>-5,85; 822,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,49; 1226,78</t>
+          <t>-5,32; 1106,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-62,01; 587,6</t>
+          <t>-48,02; 766,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 222,37</t>
+          <t>-14,79; 238,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,12; 261,14</t>
+          <t>-32,42; 234,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-46,85; 164,25</t>
+          <t>-41,39; 188,9</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 31,09</t>
+          <t>-4,52; 32,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,2; 67,71</t>
+          <t>10,21; 66,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 43,67</t>
+          <t>-1,73; 42,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 16,41</t>
+          <t>-27,8; 16,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 45,29</t>
+          <t>-10,95; 44,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-29,13; 12,5</t>
+          <t>-30,05; 11,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 19,44</t>
+          <t>-10,79; 18,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,14; 50,73</t>
+          <t>9,34; 51,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 20,59</t>
+          <t>-10,24; 20,29</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-60,44; 938,91</t>
+          <t>-44,25; 989,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>25,39; 1769,79</t>
+          <t>17,75; 2009,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,07; 1141,84</t>
+          <t>-43,65; 1067,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,39; 75,02</t>
+          <t>-58,02; 72,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 190,9</t>
+          <t>-23,81; 175,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,55; 50,95</t>
+          <t>-65,37; 48,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 139,56</t>
+          <t>-37,31; 125,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>31,47; 297,66</t>
+          <t>32,19; 311,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-34,97; 136,01</t>
+          <t>-35,8; 127,77</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 23,39</t>
+          <t>-0,74; 23,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,92; 31,46</t>
+          <t>3,13; 33,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,71; 36,06</t>
+          <t>1,73; 37,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 15,23</t>
+          <t>-6,33; 16,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,58; 30,36</t>
+          <t>3,73; 31,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 12,94</t>
+          <t>-11,9; 13,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 15,4</t>
+          <t>-0,83; 15,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,05; 26,69</t>
+          <t>8,1; 28,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 17,74</t>
+          <t>-3,14; 17,86</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 147,02</t>
+          <t>-4,51; 144,58</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>10,14; 185,73</t>
+          <t>8,77; 204,64</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2,11; 214,68</t>
+          <t>1,81; 222,99</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,27; 68,12</t>
+          <t>-18,19; 71,91</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>12,38; 127,46</t>
+          <t>12,24; 137,67</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,24; 52,1</t>
+          <t>-36,6; 56,23</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 70,76</t>
+          <t>-3,04; 70,84</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>20,67; 120,79</t>
+          <t>26,08; 133,99</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 76,84</t>
+          <t>-10,86; 77,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP09-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP09-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15,48</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22,37</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-2,79</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>10,68</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>10,55</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,47</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15,48</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22,37</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,97</t>
+          <t>5,64</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,3</t>
+          <t>0,52</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-24,8; 41,32</t>
+          <t>-11,19; 38,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,94; 48,43</t>
+          <t>-8,45; 51,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,44; 36,49</t>
+          <t>-33,01; 24,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 40,89</t>
+          <t>-21,98; 42,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 51,45</t>
+          <t>-28,9; 48,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,27; 21,66</t>
+          <t>-29,47; 35,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 33,33</t>
+          <t>-5,74; 33,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 40,25</t>
+          <t>-6,54; 41,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-26,25; 18,02</t>
+          <t>-21,68; 21,49</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>67,87%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>98,09%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-12,25%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>36,47%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>36,02%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15,27%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>67,87%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-17,41%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-5,19%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-55,02; 478,28</t>
+          <t>-36,34; 371,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-66,85; 548,66</t>
+          <t>-33,96; 435,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-60,57; 409,73</t>
+          <t>-85,15; 158,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,08; 390,29</t>
+          <t>-54,81; 456,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,02; 476,64</t>
+          <t>-64,47; 463,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,48; 139,66</t>
+          <t>-66,46; 379,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 229,39</t>
+          <t>-20,69; 212,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,54; 254,92</t>
+          <t>-18,53; 258,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-70,19; 99,24</t>
+          <t>-62,11; 126,76</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-4,74</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6,49</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13,21</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>8,65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>12,06</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>22,47</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-4,74</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,49</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,43</t>
+          <t>9,03</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15,34</t>
+          <t>11,21</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,71; 27,69</t>
+          <t>-25,25; 15,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 34,48</t>
+          <t>-15,24; 30,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 58,2</t>
+          <t>-9,48; 34,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-24,85; 14,59</t>
+          <t>-14,07; 30,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 30,72</t>
+          <t>-13,21; 37,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 32,8</t>
+          <t>-15,54; 36,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 16,63</t>
+          <t>-14,19; 16,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 26,85</t>
+          <t>-8,97; 25,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 38,67</t>
+          <t>-6,67; 28,15</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-14,31%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19,57%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39,85%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>31,29%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>43,66%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>81,32%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-14,31%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,57%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,27; 196,91</t>
+          <t>-60,85; 69,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-32,22; 231,02</t>
+          <t>-36,95; 125,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,58; 599,69</t>
+          <t>-23,24; 153,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-59,51; 66,75</t>
+          <t>-34,97; 239,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,6; 137,45</t>
+          <t>-35,31; 298,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,18; 147,81</t>
+          <t>-43,02; 239,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,44; 72,96</t>
+          <t>-36,78; 70,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,01; 116,93</t>
+          <t>-24,15; 116,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 182,76</t>
+          <t>-17,48; 124,89</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>22,71</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>30,41</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13,9</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-1,36</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-7,74</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-8,74</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>22,71</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>30,41</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,67</t>
+          <t>-10,19</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,08</t>
+          <t>5,63</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-33,77; 29,26</t>
+          <t>1,11; 43,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-42,51; 30,27</t>
+          <t>-2,07; 59,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-41,55; 26,62</t>
+          <t>-12,43; 38,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 42,63</t>
+          <t>-33,99; 27,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 59,69</t>
+          <t>-44,04; 28,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 39,69</t>
+          <t>-44,43; 24,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 33,01</t>
+          <t>-5,65; 32,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 35,22</t>
+          <t>-7,64; 36,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 27,55</t>
+          <t>-14,84; 25,89</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>131,53%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>176,09%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>80,51%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-3,42%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-19,45%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-21,97%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>131,53%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>176,09%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>-25,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-55,38; 183,55</t>
+          <t>-11,15; 805,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-76,75; 167,51</t>
+          <t>-23,43; 952,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-72,0; 168,41</t>
+          <t>-52,61; 695,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 822,1</t>
+          <t>-58,4; 175,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 1106,19</t>
+          <t>-75,87; 161,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,02; 766,87</t>
+          <t>-75,11; 144,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 238,92</t>
+          <t>-16,4; 258,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-32,42; 234,81</t>
+          <t>-25,61; 234,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-41,39; 188,9</t>
+          <t>-44,35; 183,65</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-5,92</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20,44</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-9,8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>13,13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>39,05</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>20,35</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-5,92</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>20,44</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-10,05</t>
+          <t>19,18</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,6</t>
+          <t>4,44</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 32,38</t>
+          <t>-28,33; 15,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,21; 66,14</t>
+          <t>-10,39; 47,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 42,79</t>
+          <t>-30,56; 13,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-27,8; 16,76</t>
+          <t>-7,26; 30,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 44,54</t>
+          <t>6,14; 65,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-30,05; 11,13</t>
+          <t>-0,71; 41,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 18,88</t>
+          <t>-10,43; 18,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,34; 51,0</t>
+          <t>8,03; 49,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 20,29</t>
+          <t>-11,86; 18,26</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-16,47%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>56,86%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-27,27%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>121,62%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>361,63%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>188,48%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-16,47%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>56,86%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-27,95%</t>
+          <t>177,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-44,25; 989,8</t>
+          <t>-58,93; 69,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17,75; 2009,89</t>
+          <t>-21,23; 196,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-43,65; 1067,79</t>
+          <t>-66,07; 54,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-58,02; 72,68</t>
+          <t>-55,06; 751,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 175,11</t>
+          <t>10,66; 2072,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,37; 48,61</t>
+          <t>-35,88; 1087,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-37,31; 125,21</t>
+          <t>-36,36; 122,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,19; 311,12</t>
+          <t>25,83; 299,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-35,8; 127,77</t>
+          <t>-41,28; 112,47</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,64</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>17,41</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2,35</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>11,51</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>17,72</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>15,31</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,64</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>17,41</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>10,04</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,7</t>
+          <t>5,43</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 23,05</t>
+          <t>-6,7; 15,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,13; 33,18</t>
+          <t>2,46; 30,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,73; 37,29</t>
+          <t>-11,24; 14,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 16,13</t>
+          <t>-0,73; 24,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,73; 31,16</t>
+          <t>2,15; 30,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 13,14</t>
+          <t>-3,26; 23,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 15,45</t>
+          <t>-0,29; 16,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,1; 28,92</t>
+          <t>7,24; 28,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 17,86</t>
+          <t>-3,32; 15,17</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>60,46%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>8,15%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>50,56%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>77,88%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>67,27%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>16,12%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>60,46%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 144,58</t>
+          <t>-18,99; 67,06</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8,77; 204,64</t>
+          <t>6,96; 132,31</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1,81; 222,99</t>
+          <t>-34,38; 59,91</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 71,91</t>
+          <t>-3,38; 162,37</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>12,24; 137,67</t>
+          <t>8,12; 191,37</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,6; 56,23</t>
+          <t>-12,54; 153,47</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 70,84</t>
+          <t>-1,4; 79,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>26,08; 133,99</t>
+          <t>22,02; 125,12</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 77,03</t>
+          <t>-11,43; 67,79</t>
         </is>
       </c>
     </row>
